--- a/Data/EXCEL/Transfer/dividend/20260225_0_4/01007T-dividend-20260225_0_4.xlsx
+++ b/Data/EXCEL/Transfer/dividend/20260225_0_4/01007T-dividend-20260225_0_4.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\workspaces\xls2xlxs\20260225_0_4\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Workspaces\xls2xlsx\transfer\20260225_0_4\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E9C10E03-AAD9-49CE-86EE-D74C42B3C31C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{2A620754-E170-4B79-AFE3-A0B33A751CCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4140" yWindow="576" windowWidth="16656" windowHeight="10992" xr2:uid="{6360DE94-66DB-4C56-806E-479C2D7D970E}"/>
+    <workbookView xWindow="780" yWindow="780" windowWidth="22845" windowHeight="19530" xr2:uid="{5405A986-25F4-4F38-9079-3CB985BA61B3}"/>
   </bookViews>
   <sheets>
     <sheet name="01007T-dividend-20260225_0_4" sheetId="1" r:id="rId1"/>
@@ -1589,25 +1589,25 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A6FC691F-86D2-462C-B755-0B7D883353F6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ACF22811-98E4-41D6-97BC-B05D1073695E}">
   <dimension ref="A1:R61"/>
-  <sheetFormatPr defaultRowHeight="16.2" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="5.109375" customWidth="1"/>
-    <col min="2" max="2" width="8.77734375" customWidth="1"/>
-    <col min="3" max="3" width="8.6640625" customWidth="1"/>
-    <col min="4" max="4" width="8.33203125" customWidth="1"/>
-    <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="8.33203125" customWidth="1"/>
-    <col min="7" max="9" width="8" customWidth="1"/>
-    <col min="10" max="10" width="8.33203125" customWidth="1"/>
-    <col min="11" max="13" width="8" customWidth="1"/>
-    <col min="14" max="14" width="8.33203125" customWidth="1"/>
-    <col min="15" max="17" width="8" customWidth="1"/>
-    <col min="18" max="18" width="8.44140625" customWidth="1"/>
+    <col min="1" max="1" width="6.375" customWidth="1"/>
+    <col min="2" max="2" width="10.875" customWidth="1"/>
+    <col min="3" max="3" width="10.625" customWidth="1"/>
+    <col min="4" max="4" width="10.375" customWidth="1"/>
+    <col min="5" max="5" width="9.875" customWidth="1"/>
+    <col min="6" max="6" width="10.375" customWidth="1"/>
+    <col min="7" max="9" width="9.875" customWidth="1"/>
+    <col min="10" max="10" width="10.375" customWidth="1"/>
+    <col min="11" max="13" width="9.875" customWidth="1"/>
+    <col min="14" max="14" width="10.375" customWidth="1"/>
+    <col min="15" max="17" width="9.875" customWidth="1"/>
+    <col min="18" max="18" width="12" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" s="1" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:18" s="1" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A1" s="22" t="s">
         <v>0</v>
       </c>
@@ -1635,7 +1635,7 @@
       <c r="Q1" s="31"/>
       <c r="R1" s="23"/>
     </row>
-    <row r="2" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A2" s="24" t="s">
         <v>1</v>
       </c>
@@ -1665,7 +1665,7 @@
       <c r="Q2" s="33"/>
       <c r="R2" s="34"/>
     </row>
-    <row r="3" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A3" s="24" t="s">
         <v>2</v>
       </c>
@@ -1711,7 +1711,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:18" s="3" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" s="3" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A4" s="26"/>
       <c r="B4" s="27"/>
       <c r="C4" s="7"/>
@@ -1761,7 +1761,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="5" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A5" s="38">
         <v>2025</v>
       </c>
@@ -1815,7 +1815,7 @@
         <v>3.09</v>
       </c>
     </row>
-    <row r="6" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A6" s="11" t="s">
         <v>25</v>
       </c>
@@ -1871,7 +1871,7 @@
         <v>1.65</v>
       </c>
     </row>
-    <row r="7" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
         <v>25</v>
       </c>
@@ -1927,7 +1927,7 @@
         <v>1.44</v>
       </c>
     </row>
-    <row r="8" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A8" s="40">
         <v>2024</v>
       </c>
@@ -1981,7 +1981,7 @@
         <v>2.77</v>
       </c>
     </row>
-    <row r="9" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A9" s="17" t="s">
         <v>25</v>
       </c>
@@ -2037,7 +2037,7 @@
         <v>1.38</v>
       </c>
     </row>
-    <row r="10" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A10" s="17" t="s">
         <v>25</v>
       </c>
@@ -2093,7 +2093,7 @@
         <v>1.39</v>
       </c>
     </row>
-    <row r="11" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A11" s="38">
         <v>2023</v>
       </c>
@@ -2147,7 +2147,7 @@
         <v>2.83</v>
       </c>
     </row>
-    <row r="12" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
         <v>25</v>
       </c>
@@ -2203,7 +2203,7 @@
         <v>1.47</v>
       </c>
     </row>
-    <row r="13" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A13" s="11" t="s">
         <v>25</v>
       </c>
@@ -2259,7 +2259,7 @@
         <v>1.35</v>
       </c>
     </row>
-    <row r="14" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A14" s="40">
         <v>2022</v>
       </c>
@@ -2313,7 +2313,7 @@
         <v>2.48</v>
       </c>
     </row>
-    <row r="15" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A15" s="17" t="s">
         <v>25</v>
       </c>
@@ -2369,7 +2369,7 @@
         <v>1.28</v>
       </c>
     </row>
-    <row r="16" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A16" s="17" t="s">
         <v>25</v>
       </c>
@@ -2425,7 +2425,7 @@
         <v>1.2</v>
       </c>
     </row>
-    <row r="17" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A17" s="38">
         <v>2021</v>
       </c>
@@ -2479,7 +2479,7 @@
         <v>2.2000000000000002</v>
       </c>
     </row>
-    <row r="18" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A18" s="11" t="s">
         <v>25</v>
       </c>
@@ -2535,7 +2535,7 @@
         <v>1.1200000000000001</v>
       </c>
     </row>
-    <row r="19" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A19" s="11" t="s">
         <v>25</v>
       </c>
@@ -2591,7 +2591,7 @@
         <v>1.08</v>
       </c>
     </row>
-    <row r="20" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A20" s="40">
         <v>2020</v>
       </c>
@@ -2645,7 +2645,7 @@
         <v>2.31</v>
       </c>
     </row>
-    <row r="21" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A21" s="17" t="s">
         <v>25</v>
       </c>
@@ -2701,7 +2701,7 @@
         <v>1.19</v>
       </c>
     </row>
-    <row r="22" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A22" s="17" t="s">
         <v>25</v>
       </c>
@@ -2757,7 +2757,7 @@
         <v>1.1200000000000001</v>
       </c>
     </row>
-    <row r="23" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A23" s="38">
         <v>2019</v>
       </c>
@@ -2811,7 +2811,7 @@
         <v>2.57</v>
       </c>
     </row>
-    <row r="24" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A24" s="11" t="s">
         <v>25</v>
       </c>
@@ -2867,7 +2867,7 @@
         <v>1.1599999999999999</v>
       </c>
     </row>
-    <row r="25" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
         <v>25</v>
       </c>
@@ -2923,7 +2923,7 @@
         <v>1.4</v>
       </c>
     </row>
-    <row r="26" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A26" s="40">
         <v>2018</v>
       </c>
@@ -2977,7 +2977,7 @@
         <v>2.94</v>
       </c>
     </row>
-    <row r="27" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A27" s="17" t="s">
         <v>25</v>
       </c>
@@ -3033,7 +3033,7 @@
         <v>1.43</v>
       </c>
     </row>
-    <row r="28" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A28" s="17" t="s">
         <v>25</v>
       </c>
@@ -3089,7 +3089,7 @@
         <v>1.51</v>
       </c>
     </row>
-    <row r="29" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A29" s="38">
         <v>2017</v>
       </c>
@@ -3143,7 +3143,7 @@
         <v>3.17</v>
       </c>
     </row>
-    <row r="30" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A30" s="11" t="s">
         <v>25</v>
       </c>
@@ -3199,7 +3199,7 @@
         <v>1.67</v>
       </c>
     </row>
-    <row r="31" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A31" s="11" t="s">
         <v>25</v>
       </c>
@@ -3255,7 +3255,7 @@
         <v>1.49</v>
       </c>
     </row>
-    <row r="32" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A32" s="40">
         <v>2016</v>
       </c>
@@ -3309,7 +3309,7 @@
         <v>2.68</v>
       </c>
     </row>
-    <row r="33" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A33" s="17" t="s">
         <v>25</v>
       </c>
@@ -3365,7 +3365,7 @@
         <v>1.35</v>
       </c>
     </row>
-    <row r="34" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A34" s="17" t="s">
         <v>25</v>
       </c>
@@ -3421,7 +3421,7 @@
         <v>1.33</v>
       </c>
     </row>
-    <row r="35" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A35" s="38">
         <v>2015</v>
       </c>
@@ -3475,7 +3475,7 @@
         <v>2.82</v>
       </c>
     </row>
-    <row r="36" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A36" s="11" t="s">
         <v>25</v>
       </c>
@@ -3531,7 +3531,7 @@
         <v>1.45</v>
       </c>
     </row>
-    <row r="37" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A37" s="11" t="s">
         <v>25</v>
       </c>
@@ -3587,7 +3587,7 @@
         <v>1.36</v>
       </c>
     </row>
-    <row r="38" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A38" s="40">
         <v>2014</v>
       </c>
@@ -3641,7 +3641,7 @@
         <v>2.89</v>
       </c>
     </row>
-    <row r="39" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A39" s="17" t="s">
         <v>25</v>
       </c>
@@ -3697,7 +3697,7 @@
         <v>1.42</v>
       </c>
     </row>
-    <row r="40" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A40" s="17" t="s">
         <v>25</v>
       </c>
@@ -3753,7 +3753,7 @@
         <v>1.48</v>
       </c>
     </row>
-    <row r="41" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A41" s="38">
         <v>2013</v>
       </c>
@@ -3807,7 +3807,7 @@
         <v>2.48</v>
       </c>
     </row>
-    <row r="42" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A42" s="11" t="s">
         <v>25</v>
       </c>
@@ -3863,7 +3863,7 @@
         <v>1.28</v>
       </c>
     </row>
-    <row r="43" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A43" s="11" t="s">
         <v>25</v>
       </c>
@@ -3919,7 +3919,7 @@
         <v>1.19</v>
       </c>
     </row>
-    <row r="44" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A44" s="40">
         <v>2012</v>
       </c>
@@ -3973,7 +3973,7 @@
         <v>2.78</v>
       </c>
     </row>
-    <row r="45" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A45" s="17" t="s">
         <v>25</v>
       </c>
@@ -4029,7 +4029,7 @@
         <v>1.33</v>
       </c>
     </row>
-    <row r="46" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A46" s="17" t="s">
         <v>25</v>
       </c>
@@ -4085,7 +4085,7 @@
         <v>1.45</v>
       </c>
     </row>
-    <row r="47" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A47" s="38">
         <v>2011</v>
       </c>
@@ -4139,7 +4139,7 @@
         <v>3.61</v>
       </c>
     </row>
-    <row r="48" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A48" s="11" t="s">
         <v>25</v>
       </c>
@@ -4195,7 +4195,7 @@
         <v>1.73</v>
       </c>
     </row>
-    <row r="49" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A49" s="11" t="s">
         <v>25</v>
       </c>
@@ -4251,7 +4251,7 @@
         <v>1.88</v>
       </c>
     </row>
-    <row r="50" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A50" s="40">
         <v>2010</v>
       </c>
@@ -4305,7 +4305,7 @@
         <v>3.4</v>
       </c>
     </row>
-    <row r="51" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A51" s="17" t="s">
         <v>25</v>
       </c>
@@ -4361,7 +4361,7 @@
         <v>1.65</v>
       </c>
     </row>
-    <row r="52" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A52" s="17" t="s">
         <v>25</v>
       </c>
@@ -4417,7 +4417,7 @@
         <v>1.75</v>
       </c>
     </row>
-    <row r="53" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A53" s="38">
         <v>2009</v>
       </c>
@@ -4471,7 +4471,7 @@
         <v>4.03</v>
       </c>
     </row>
-    <row r="54" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A54" s="11" t="s">
         <v>25</v>
       </c>
@@ -4527,7 +4527,7 @@
         <v>1.88</v>
       </c>
     </row>
-    <row r="55" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A55" s="11" t="s">
         <v>25</v>
       </c>
@@ -4583,7 +4583,7 @@
         <v>2.16</v>
       </c>
     </row>
-    <row r="56" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A56" s="40">
         <v>2008</v>
       </c>
@@ -4637,7 +4637,7 @@
         <v>4.4800000000000004</v>
       </c>
     </row>
-    <row r="57" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A57" s="17" t="s">
         <v>25</v>
       </c>
@@ -4693,7 +4693,7 @@
         <v>2.63</v>
       </c>
     </row>
-    <row r="58" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A58" s="17" t="s">
         <v>25</v>
       </c>
@@ -4749,7 +4749,7 @@
         <v>1.85</v>
       </c>
     </row>
-    <row r="59" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A59" s="38">
         <v>2007</v>
       </c>
@@ -4803,7 +4803,7 @@
         <v>2.84</v>
       </c>
     </row>
-    <row r="60" spans="1:18" s="9" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:18" s="9" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A60" s="11" t="s">
         <v>25</v>
       </c>
@@ -4859,7 +4859,7 @@
         <v>2.84</v>
       </c>
     </row>
-    <row r="61" spans="1:18" s="15" customFormat="1" ht="13.8" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:18" s="15" customFormat="1" ht="14.25" x14ac:dyDescent="0.25">
       <c r="A61" s="40" t="s">
         <v>81</v>
       </c>
